--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0094.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0094.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Infernal Descent</t>
+          <t>Hạ Giới Sa Đọa</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Bamboo Flask</t>
+          <t>Bình Tre</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Iron Weight</t>
+          <t>Gánh Nặng Thép</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bamboo Flute</t>
+          <t>Sáo Tre</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Portable Frequency Cassette Recorder - Prototype</t>
+          <t>Máy Ghi Tần Số Di Động - Mẫu Thử Nghiệm</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>"Sweet Dreams"</t>
+          <t>"Giấc Mộng Ngọt Ngào"</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>"The First Blood Pact"</t>
+          <t>"Hiệp Ước Máu Đầu Tiên"</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Tempered</t>
+          <t>Tôi luyện</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Concealed</t>
+          <t>Ẩn Giấu</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Unsheathed</t>
+          <t>Đã Rút Kiếm</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Shattered</t>
+          <t>Đã vỡ tan</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Reforged</t>
+          <t>Đã tái tạo</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Ngày của Thợ Săn</t>
+          <t>Ngày Của Thợ Săn</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Of a Childhood Long Gone</t>
+          <t>Tuổi Thơ Đã Xa</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Angel's Ashes</t>
+          <t>Tro Tàn Thiên Thần</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Skies Within</t>
+          <t>Bầu Trời Trong Tim</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A Return Long Awaited</t>
+          <t>Trở Về Sau Dài Ngày Chờ Đợi</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Không thể tham gia sự kiện này trong Chế độ Hợp Tác</t>
+          <t>Không thể tham gia sự kiện này trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Chiến thuật đã chọn</t>
+          <t>Chiến Thuật Đã Chọn</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Chưa chọn Resonator nào</t>
+          <t>Chưa chọn Resonator</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Không còn gì để lần theo</t>
+          <t>Không còn dấu vết gì để lần theo nữa.</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Hoàng Hôn trên Bờm Vàng</t>
+          <t>Hoàng hôn trên Bờm Vàng</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Tiếng Gầm Cuối Cùng của Sư Tử Cái</t>
+          <t>Tiếng Gầm Cuối Của Sư Tử Cái</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Cửa hàng đã làm mới</t>
+          <t>Đã làm mới cửa hàng</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Good-natured</t>
+          <t>Tốt bụng</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Bouquet</t>
+          <t>Bó Hoa</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Playtime</t>
+          <t>Thời gian diễn</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Provoke</t>
+          <t>Khiêu khích</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>Ôi!</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Let Me See</t>
+          <t>Để ta xem nào</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Đang vẽ...</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Không Money</t>
+          <t>Hết Tiền</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Blushing</t>
+          <t>Đỏ Mặt</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>On It</t>
+          <t>Để tao lo</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Studying</t>
+          <t>Đang học</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Tốt lắm</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Analyzing</t>
+          <t>Đang phân tích</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Aim</t>
+          <t>Ngắm</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>I Have Monnaie</t>
+          <t>Ta Có Monnaie</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Elegant</t>
+          <t>Thanh Lịch</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Drink Tea</t>
+          <t>Uống trà</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Smirk</t>
+          <t>Nụ cười khinh bỉ</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Got Bạn</t>
+          <t>Bắt Được Rồi</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Interesting</t>
+          <t>Thú vị thật</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Look Around</t>
+          <t>Nhìn Xung Quanh</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Turn Off</t>
+          <t>Tắt</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Reliable</t>
+          <t>Đáng tin cậy</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>CHẠY!</t>
+          <t>CHẠY ĐI!</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Wobble</t>
+          <t>Lảo đảo</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Let Me See</t>
+          <t>Để ta xem nào</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Peek</t>
+          <t>Nhìn Lén</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Cúi chào</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Upset</t>
+          <t>Bực Mình</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Wink</t>
+          <t>Nháy Mắt</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Sunglasses</t>
+          <t>Kính râm</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Exclamation Mark</t>
+          <t>Dấu chấm than</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Question Mark</t>
+          <t>Dấu hỏi</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Flame Undying</t>
+          <t>Lửa Bất Diệt</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Blade Within Bamboo</t>
+          <t>Kiếm Ẩn Trong Tre</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Không thể thực hiện hành động này ở trạng thái hiện tại</t>
+          <t>Hiện không thể thực hiện hành động này</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Cửa hàng Cleanup</t>
+          <t>Dọn Dẹp Cửa Hàng</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Lighting Design</t>
+          <t>Thiết Kế Ánh Sáng</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Cửa hàng Signboard</t>
+          <t>Bảng Hiệu Cửa Hàng</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Fresh Ground</t>
+          <t>Cà Phê Mới Xay</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Craft Workshop</t>
+          <t>Xưởng Chế Tạo</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Premium Vật tư I</t>
+          <t>Gói Vật Tư Cao Cấp I</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Cửa hàng Promotion I</t>
+          <t>Ưu Đãi Cửa Hàng I</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Good Reputation I</t>
+          <t>Danh Tiếng Tốt I</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Counter Extension</t>
+          <t>Kéo dài phản đòn</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Dessert Baking</t>
+          <t>Làm Bánh Tráng Miệng</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Indoor Greenery</t>
+          <t>Cây Cảnh Trong Nhà</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Premium Vật tư II</t>
+          <t>Gói Vật Tư Cao Cấp II</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Cửa hàng Promotion II</t>
+          <t>Ưu Đãi Cửa Hàng II</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Good Reputation II</t>
+          <t>Danh Tiếng Tốt II</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Exterior Design</t>
+          <t>Thiết Kế Ngoại Thất</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Honami Floristry</t>
+          <t>Nghệ thuật Cắm hoa Honami</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Storage Nâng cấp</t>
+          <t>Nâng Cấp Kho Lưu Trữ</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Table Decor</t>
+          <t>Trang Trí Bàn</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Premium Vật tư III</t>
+          <t>Vật Phẩm Cao Cấp III</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Cửa hàng Promotion II</t>
+          <t>Ưu Đãi Cửa Hàng II</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Good Reputation III</t>
+          <t>Danh Tiếng Tốt III</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Trang Trí Quán Cà Phê</t>
+          <t>Trang trí quán cà phê</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Hồ Sơ Vụ Án Namipon</t>
+          <t>Hồ Sơ Bí Mật Namipon</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Side Objective Income</t>
+          <t>Thu nhập Nhiệm vụ Phụ</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Storage Expansion I</t>
+          <t>Mở Rộng Kho Lưu Trữ I</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Rice Dango Bonus</t>
+          <t>Thưởng Bánh Dango Gạo</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Waveworn Resistance I</t>
+          <t>Kháng Sóng Cấp I</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Blind Box Discount</t>
+          <t>Hộp Ngẫu Nhiên Giảm Giá</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Storage Expansion II</t>
+          <t>Mở Rộng Kho Lưu Trữ II</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Evacuation Insurance</t>
+          <t>Bảo hiểm Sơ tán</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Waveworn Resistance II</t>
+          <t>Kháng Sóng Cấp II</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Thư viện Unlock</t>
+          <t>Mở Khóa Triển Lãm</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Sticker Nâng cấp</t>
+          <t>Nâng cấp Sticker</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Storage Expansion III</t>
+          <t>Mở Rộng Kho Lưu Trữ III</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Luck Enhancement</t>
+          <t>Tăng Cường May Mắn</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Waveworn Resistance III</t>
+          <t>Kháng Sóng Cấp III</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Dọn sạch Khu Dân Cư</t>
+          <t>Dọn sạch Khu Dân Cư.</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Clear Hanakage Underground Street</t>
+          <t>Dọn sạch Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Clear Honami Central Park</t>
+          <t>Dọn sạch Công Viên Trung Tâm Honami</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách Tháp Neon một lần</t>
+          <t>Hoàn thành thử thách Neon Tower một lần</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 1.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 1.000 Bánh Gạo Dango</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 20.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 20.000 Bánh Gạo Dango</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 40.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 40.000 Bánh Dango Gạo.</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 60.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 60.000 Rice Dango</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 100.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 100.000 Bánh Dango Gạo</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 150.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 150.000 Bánh Gạo Dango</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 250.000 Bánh Gạo Dango</t>
+          <t>Nhận tổng cộng 250.000 Bánh Gạo Dango.</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 350.000 Bánh Gạo Dango</t>
+          <t>Tổng cộng thu thập 350.000 Bánh Dango Gạo.</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 450.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 450.000 Bánh Gạo Dango</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 650.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 650.000 Rice Dango</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 850.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 850.000 Bánh Dango Gạo.</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 1.200.000 Bánh Gạo Dango</t>
+          <t>Thu thập tổng cộng 1.200.000 Bánh Gạo Dango</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Nhiệm vụ này hiện đang bị chặn</t>
+          <t>Nhiệm vụ này hiện đang bị chặn.</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Buff</t>
+          <t>Tăng Cường</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Multi-Stage DMG</t>
+          <t>DMG đa giai đoạn</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Single-Stage DMG</t>
+          <t>Sát Thương Một Giai Đoạn</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Namipon Projectile</t>
+          <t>Đạn Namipon</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>DoT</t>
+          <t>Sát thương theo thời gian</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Tuner *50</t>
+          <t>Điều Chỉnh Giả *50</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Modifier *5</t>
+          <t>Bộ điều chỉnh *5</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Phantom: The False Sovereign</t>
+          <t>Phantom: Quân Vương Giả</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>By Moon's Grace</t>
+          <t>Nhờ Ân Huệ của Mặt Trăng</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi giải quyết dị thường tại Khu phố Sakura</t>
+          <t>Mở khóa sau khi giải quyết bất thường tại Khu Sakura</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi giải quyết dị thường tại Hành lang Meishin</t>
+          <t>Mở khóa sau khi giải quyết bất thường tại Hành Lang Meishin</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi giải quyết dị thường tại Đường hầm ngầm Hanakage</t>
+          <t>Mở khóa sau khi giải quyết bất thường tại Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Cửa hàng Cleanup Unlocked</t>
+          <t>Đã Mở Khóa Dọn Dẹp Cửa Hàng</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Lighting Design Unlocked</t>
+          <t>Đã Mở Khóa Thiết Kế Ánh Sáng</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Cafe Sign Unlocked</t>
+          <t>Biển Hiệu Quán Cà Phê Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Ground Coffee Unlocked</t>
+          <t>Đã mở khóa Cà phê Mặt đất</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Crafting Table Unlocked</t>
+          <t>Đã mở khóa Bàn chế tác</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Premium Vật tư I Unlocked</t>
+          <t>Gói Vật Tư Cao Cấp I Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Cửa hàng Promotion I Unlocked</t>
+          <t>Đã Mở Khóa Ưu Đãi Cửa Hàng I</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Good Reputation I Unlocked</t>
+          <t>Đã Mở Khóa Danh Tiếng Tốt I</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Bar Counter Expansion Unlocked</t>
+          <t>Mở khóa mở rộng Quầy Bar</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>New Board Installation Unlocked</t>
+          <t>Bảng Điều Khiển Mới Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Dessert Baking Unlocked</t>
+          <t>Đã Mở Khóa: Làm Bánh Ngọt</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Indoor Greening Unlocked</t>
+          <t>Mở Khóa Trồng Cây Trong Nhà</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Premium Vật tư II Unlocked</t>
+          <t>Gói Vật Tư Cao Cấp II Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Cửa hàng Promotion II Unlocked</t>
+          <t>Đã Mở Khóa Ưu Đãi Cửa Hàng II</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Good Reputation II Unlocked</t>
+          <t>Đã Mở Khóa Danh Tiếng Tốt II</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Outdoor Design Unlocked</t>
+          <t>Mở khóa Thiết kế Ngoại thất</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Honami Floristry Unlocked</t>
+          <t>Mở khóa: Nghệ thuật Cắm hoa Honami</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Storage Nâng cấp Unlocked</t>
+          <t>Đã Mở Khóa Nâng Cấp Kho Lưu Trữ</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Table Decor Unlocked</t>
+          <t>Đã Mở Khóa Trang Trí Bàn</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Premium Vật tư III Unlocked</t>
+          <t>Đã Mở Khóa Vật Phẩm Cao Cấp III</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Cửa hàng Promotion III Unlocked</t>
+          <t>Đã Mở Khóa Ưu Đãi Cửa Hàng III</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Good Reputation III Unlocked</t>
+          <t>Đã Mở Khóa Danh Tiếng Tốt III</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Phần thưởng thêm</t>
+          <t>Phần Thưởng Bổ Sung</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Nói chuyện với cô gái nghiên cứu tấm áp phích</t>
+          <t>Nói chuyện với cô gái đang nghiên cứu tấm áp phích</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Gỡ bỏ áp phích Namipon tại Khu phố Sakura</t>
+          <t>Gỡ tấm áp phích Namipon ở Khu phố Sakura đi</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Gỡ bỏ áp phích Namipon gần công viên dân cư</t>
+          <t>Gỡ tấm áp phích Namipon gần công viên dân cư đi</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Kích hoạt Máy Capsule bị nhiễm Lament một lần</t>
+          <t>Kích hoạt Máy Trạm Nhiễm Bi Ai một lần</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Tiêu diệt dị thường tại bất kỳ khu vực nào</t>
+          <t>Loại bỏ dị thường ở một khu vực bất kỳ</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Thanh tẩy Khu vực bị nhiễm Lament</t>
+          <t>Thanh tẩy Khu Vực Nhiễm Than Thở</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Nói chuyện với cô gái nghiên cứu tấm áp phích</t>
+          <t>Nói chuyện với cô gái đang nghiên cứu tấm áp phích</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Gỡ bỏ áp phích Namipon tại Trung tâm Hội nghị Honami</t>
+          <t>Gỡ tấm áp phích Namipon ở Trung tâm Hội nghị Honami đi</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Gỡ bỏ áp phích Namipon tại Hành lang Meishin</t>
+          <t>Gỡ tấm áp phích Namipon ở Hành lang Meishin đi</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Loại bỏ dị thường ở đường phố ngầm: Thundering Mephis</t>
+          <t>Tiêu diệt dị thường ở đường ngầm: Thundering Mephis</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Hạ gục tấm áp phích Namipon ở Hanakage Underground Street</t>
+          <t>Hạ tấm áp phích Namipon ở Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Nói chuyện với cô gái nghiên cứu tấm áp phích</t>
+          <t>Nói chuyện với cô gái đang nghiên cứu tấm áp phích</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Loại bỏ dị thường ở công viên: Feilian Beringal</t>
+          <t>Tiêu diệt dị thường ở công viên: Feilian Beringal</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Nói chuyện với cô gái nghiên cứu tấm áp phích</t>
+          <t>Nói chuyện với cô gái đang nghiên cứu tấm áp phích</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Hạ gục tấm áp phích Namipon ở Honami Central Park</t>
+          <t>Hạ tấm áp phích Namipon ở Công viên Trung tâm Honami</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Hạ gục tấm áp phích Namipon ở Honami Central Park</t>
+          <t>Hạ tấm áp phích Namipon ở Công viên Trung tâm Honami</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Tiny KU-Roro</t>
+          <t>KU-Roro Nhỏ Xíu</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Ngôi sao của Solaris</t>
+          <t>Ngôi Sao Solaris</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Weird Swim Ring</t>
+          <t>Phao bơi kỳ lạ</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Secret Edition Namipon Plushie</t>
+          <t>Gấu Bông Namipon Phiên Bản Bí Mật</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Miniature Neon Tower</t>
+          <t>Tháp Neon thu nhỏ</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Handcrafted Wind Chime</t>
+          <t>Chuông gió thủ công</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Namipon Lantern</t>
+          <t>Đèn lồng Namipon</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Nước Uống Có Ga Namipon Kỷ Niệm 30 Năm</t>
+          <t>Nước Có Gas Của Namipon - Phiên Bản Kỷ Niệm 30 Năm</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Lon Nước Uống của Giáo Sư Namipon</t>
+          <t>Lon Nước Uống của Giáo sư Namipon</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Pirate Ship Model</t>
+          <t>Mô hình Tàu Cướp Biển</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Sakura Umbrella</t>
+          <t>Ô Sakura</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Fish Windsock</t>
+          <t>Cá Gió</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Corrupted: Flautist</t>
+          <t>Nhiễm Độc: Flautist</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Corrupted: Tambourinist</t>
+          <t>Nhiễm Độc: Tambourinist</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Corrupted: Chop Chop</t>
+          <t>Nhiễm Độc: Chop Chop</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Corrupted: Lumiscale Construct</t>
+          <t>Nhiễm Độc: Lumiscale Construct</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Vinh Quang Nhân Loại</t>
+          <t>Vinh Quang của Nhân Loại</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Săn Lùng Ánh Sáng</t>
+          <t>Săn Ánh Sáng</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Doomsday Revelation</t>
+          <t>Lời Tiên Tri Tận Thế</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Should Darkness Lie Ahead</t>
+          <t>Nếu Phía Trước Là Bóng Tối</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Bóp Cò</t>
+          <t>Kéo cò</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>A Dawn Without Divinity</t>
+          <t>Bình Minh Vô Thần</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Nguồn Cội Của Quần Đảo</t>
+          <t>Nguồn Gốc Hòn Đảo</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Khởi Đầu Cuộc Săn Vĩnh Cửu</t>
+          <t>Bắt đầu Cuộc Săn Bất Tận</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Bình Minh Lên Trên Những Con Sóng U Ám</t>
+          <t>Bình Minh Trên Bóng Tối Dâng Trào</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Rinascita Chương II: Quá Khứ Sẽ Luôn Trở Lại</t>
+          <t>Chương II Rinascita: Những Điều Đã Qua Sẽ Luôn Trở Lại</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Rinascita Chương II: Bình Minh Lên Trên Những Con Sóng U Ám</t>
+          <t>Chương II: Dawn Breaks on Dark Tides</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Rinascita Chương II: Kẻ Lạ Mặt Ở Vùng Đất Lạ</t>
+          <t>Chương II: Rinascita - Kẻ Lạ Nơi Đất Khách</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Nút điều kiện bị khóa</t>
+          <t>Điểm nút Điều kiện tiên quyết bị khóa</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Insufficient Rice Dangos</t>
+          <t>Bánh Dango gạo không đủ</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Dễ thôi</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Khó</t>
+          <t>Khó khăn</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Kỷ lục thông quan cấp hiện tại</t>
+          <t>Kỷ Lục Vượt Ải Hiện Tại</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Book Namipon Shuttle</t>
+          <t>Tàu Con Thoi Namipon Sách</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Đã mở khóa tất cả nhiệm vụ giai đoạn</t>
+          <t>Tất cả nhiệm vụ sân khấu đã được mở khóa</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Quick Nâng cấp</t>
+          <t>Nâng Cấp Nhanh</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Convert</t>
+          <t>Chuyển Đổi</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Insufficient Shell Credits</t>
+          <t>Không đủ Shell Credit</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Obtain</t>
+          <t>Nhận Được</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Đã tổng hợp vật liệu</t>
+          <t>Vật liệu tổng hợp thành công</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Bạn chưa chọn đủ Buff</t>
+          <t>Cậu chưa chọn đủ Buff</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Chọn Vũ khí</t>
+          <t>Chọn Vũ Khí</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Chọn Vật phẩm</t>
+          <t>Chọn vật phẩm</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Phần thưởng thêm</t>
+          <t>Phần Thưởng Bổ Sung</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Apply Suggested Deck</t>
+          <t>Áp dụng Bộ Thẻ Đề Xuất</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>&lt;color=#586778&gt;Điều Kỳ Lạ Ở Honami&lt;/color&gt;</t>
+          <t>&lt;color=#586778&gt;Những Điều Kỳ Lạ Ở Honami&lt;/color&gt;</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đã chuyển đổi vật liệu</t>
+          <t>Vật liệu đã chuyển hóa</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Không thể nhận nhiệm vụ trong Chế độ Tập trung</t>
+          <t>Không thể nhận nhiệm vụ khi đang ở Chế Độ Tập Trung</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Required Download</t>
+          <t>Cần tải xuống</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Optional Download</t>
+          <t>Tải Xuống Tùy Chọn</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Expansion Download</t>
+          <t>Tải Gói Mở rộng</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Core Assets</t>
+          <t>Tài Nguyên Cốt Lõi</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Expansion Assets</t>
+          <t>Tài sản Mở rộng</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Tải xuống bằng dữ liệu di động</t>
+          <t>Tải bằng dữ liệu di động</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Space Cleared</t>
+          <t>Khu vực đã được dọn sạch</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Kingslayer</t>
+          <t>Kẻ Sát Vương</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>The Last Moon Fang</t>
+          <t>Nanh Trăng Cuối Cùng</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Được Thần Linh Và Ác Quỷ Chú Ý</t>
+          <t>Được thần linh và ác quỷ lắng nghe.</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Calamity Ender</t>
+          <t>Kẻ Diệt Tai Họa</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả thử thách trong Chiến thuật Hologram: Tai ương</t>
+          <t>Hoàn thành tất cả thử thách trong Tactical Hologram: Calamity.</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả thử thách trong Chiến thuật Hologram: Tai ương</t>
+          <t>Hoàn thành tất cả thử thách trong Tactical Hologram: Calamity.</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Đắm Chìm Trong Đau Đớn</t>
+          <t>Ngập Tràn Nỗi Đau</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả thử thách trong Chiến thuật Hologram: Nỗi Đau Ảo Giác</t>
+          <t>Hoàn thành tất cả thử thách trong Tactical Hologram: Phantom Pain.</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả thử thách trong Tactical Hologram: Phantom Pain</t>
+          <t>Hoàn thành tất cả thử thách trong Tactical Hologram: Phantom Pain.</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Colorful Dawn</t>
+          <t>Bình Minh Rực Rỡ</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Mỏ neo của Lý tưởng</t>
+          <t>Mỏ Neo Lý Tưởng</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Quy luật của những Vì sao</t>
+          <t>Luật của Vì Sao</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Đạt 5.000 Điểm Hành trình trong "Starpaths Intertwined"</t>
+          <t>Đạt 5.000 Điểm Hành Trình trong "Những Con Đường Sao Đan Xen"</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Đạt 5.000 Điểm Hành trình trong "Starpaths Intertwined"</t>
+          <t>Đạt 5.000 Điểm Hành Trình trong "Những Con Đường Sao Đan Xen"</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Roving Lodestar</t>
+          <t>Ngôi Sao Dẫn Lối Lang Thang</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Đôi cánh Mùa xuân</t>
+          <t>Đôi Cánh Mùa Xuân</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Golden Diagnosis</t>
+          <t>Chẩn Đoán Vàng</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Matrix Ranger</t>
+          <t>Lính Tuần Tra Ma Trận</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Fan Club Rescue</t>
+          <t>Giải Cứu Câu Lạc Bộ Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Fan Club Rescue</t>
+          <t>Giải Cứu Câu Lạc Bộ Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Fan Club Rescue</t>
+          <t>Giải Cứu Câu Lạc Bộ Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Fan Club Rescue</t>
+          <t>Giải Cứu Câu Lạc Bộ Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Fan Club Rescue</t>
+          <t>Giải Cứu Câu Lạc Bộ Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Fan Club Rescue</t>
+          <t>Giải Cứu Câu Lạc Bộ Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Lahai-Roi Ranked Tournament</t>
+          <t>Giải Đấu Xếp Hạng Lahai-Roi</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
